--- a/files/Countries_Prod_TC.xlsx
+++ b/files/Countries_Prod_TC.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -41,12 +41,12 @@
     <t xml:space="preserve">USA</t>
   </si>
   <si>
+    <t xml:space="preserve">Canada</t>
+  </si>
+  <si>
     <t xml:space="preserve">China</t>
   </si>
   <si>
-    <t xml:space="preserve">Canada</t>
-  </si>
-  <si>
     <t xml:space="preserve">Australia</t>
   </si>
   <si>
@@ -56,57 +56,57 @@
     <t xml:space="preserve">Italy</t>
   </si>
   <si>
+    <t xml:space="preserve">Turkey</t>
+  </si>
+  <si>
     <t xml:space="preserve">Spain</t>
   </si>
   <si>
-    <t xml:space="preserve">Turkey</t>
-  </si>
-  <si>
     <t xml:space="preserve">Japan</t>
   </si>
   <si>
     <t xml:space="preserve">Netherlands</t>
   </si>
   <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Zealand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
     <t xml:space="preserve">Brazil</t>
   </si>
   <si>
-    <t xml:space="preserve">Sweden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Zealand</t>
-  </si>
-  <si>
     <t xml:space="preserve">South Korea</t>
   </si>
   <si>
     <t xml:space="preserve">Ireland</t>
   </si>
   <si>
+    <t xml:space="preserve">Belgium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iran</t>
+  </si>
+  <si>
     <t xml:space="preserve">Norway</t>
   </si>
   <si>
-    <t xml:space="preserve">Belgium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iran</t>
+    <t xml:space="preserve">Indonesia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Georgia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
   </si>
   <si>
     <t xml:space="preserve">India</t>
   </si>
   <si>
-    <t xml:space="preserve">Indonesia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Georgia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Saudi Arabia</t>
   </si>
   <si>
@@ -122,54 +122,54 @@
     <t xml:space="preserve">Malaysia</t>
   </si>
   <si>
+    <t xml:space="preserve">Singapore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greece</t>
+  </si>
+  <si>
     <t xml:space="preserve">South Africa</t>
   </si>
   <si>
-    <t xml:space="preserve">Greece</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Singapore</t>
+    <t xml:space="preserve">Denmark</t>
   </si>
   <si>
     <t xml:space="preserve">Switzerland</t>
   </si>
   <si>
-    <t xml:space="preserve">Denmark</t>
-  </si>
-  <si>
     <t xml:space="preserve">Austria</t>
   </si>
   <si>
+    <t xml:space="preserve">Czech Republic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
     <t xml:space="preserve">Portugal</t>
   </si>
   <si>
-    <t xml:space="preserve">Colombia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czech Republic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poland</t>
-  </si>
-  <si>
     <t xml:space="preserve">Romania</t>
   </si>
   <si>
+    <t xml:space="preserve">Lithuania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thailand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UAE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Estonia</t>
   </si>
   <si>
-    <t xml:space="preserve">Lithuania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thailand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UAE</t>
-  </si>
-  <si>
     <t xml:space="preserve">Iceland</t>
   </si>
   <si>
@@ -185,40 +185,31 @@
     <t xml:space="preserve">Tanzania</t>
   </si>
   <si>
+    <t xml:space="preserve">Ecuador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egypt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazakhstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morocco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serbia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sri Lanka</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tunisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecuador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egypt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kazakhstan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morocco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serbia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovakia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sri Lanka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vietnam</t>
   </si>
 </sst>
 </file>
@@ -578,25 +569,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>2104</v>
+        <v>2089</v>
       </c>
       <c r="C2" t="n">
-        <v>0.61145</v>
+        <v>0.625824</v>
       </c>
       <c r="D2" t="n">
-        <v>2001</v>
+        <v>1976</v>
       </c>
       <c r="E2" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F2" t="n">
-        <v>0.049</v>
+        <v>0.0541</v>
       </c>
       <c r="G2" t="n">
-        <v>52606</v>
+        <v>51828</v>
       </c>
       <c r="H2" t="n">
-        <v>24.77</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="3">
@@ -604,25 +595,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="C3" t="n">
-        <v>0.041848</v>
+        <v>0.038945</v>
       </c>
       <c r="D3" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1736</v>
+        <v>0.1615</v>
       </c>
       <c r="G3" t="n">
-        <v>1351</v>
+        <v>2093</v>
       </c>
       <c r="H3" t="n">
-        <v>9.19</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="4">
@@ -630,25 +621,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03807</v>
+        <v>0.036848</v>
       </c>
       <c r="D4" t="n">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1527</v>
+        <v>0.2195</v>
       </c>
       <c r="G4" t="n">
-        <v>2247</v>
+        <v>1295</v>
       </c>
       <c r="H4" t="n">
-        <v>17.02</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="5">
@@ -656,25 +647,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03313</v>
+        <v>0.033553</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E5" t="n">
         <v>30</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2632</v>
+        <v>0.2679</v>
       </c>
       <c r="G5" t="n">
-        <v>2042</v>
+        <v>2031</v>
       </c>
       <c r="H5" t="n">
-        <v>17.91</v>
+        <v>18.13</v>
       </c>
     </row>
     <row r="6">
@@ -682,25 +673,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C6" t="n">
-        <v>0.032549</v>
+        <v>0.031456</v>
       </c>
       <c r="D6" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2768</v>
+        <v>0.2762</v>
       </c>
       <c r="G6" t="n">
-        <v>2493</v>
+        <v>2389</v>
       </c>
       <c r="H6" t="n">
-        <v>22.26</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="7">
@@ -708,25 +699,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02383</v>
+        <v>0.023667</v>
       </c>
       <c r="D7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" t="n">
-        <v>0.439</v>
+        <v>0.443</v>
       </c>
       <c r="G7" t="n">
-        <v>918</v>
+        <v>897</v>
       </c>
       <c r="H7" t="n">
-        <v>10.93</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="8">
@@ -734,25 +725,25 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>0.019471</v>
+        <v>0.020371</v>
       </c>
       <c r="D8" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3731</v>
+        <v>0.0735</v>
       </c>
       <c r="G8" t="n">
-        <v>827</v>
+        <v>665</v>
       </c>
       <c r="H8" t="n">
-        <v>12.34</v>
+        <v>9.64</v>
       </c>
     </row>
     <row r="9">
@@ -760,25 +751,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>0.019471</v>
+        <v>0.018874</v>
       </c>
       <c r="D9" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0597</v>
+        <v>0.381</v>
       </c>
       <c r="G9" t="n">
-        <v>665</v>
+        <v>758</v>
       </c>
       <c r="H9" t="n">
-        <v>9.64</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="10">
@@ -786,25 +777,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>0.016856</v>
+        <v>0.015578</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E10" t="n">
         <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1379</v>
+        <v>0.1538</v>
       </c>
       <c r="G10" t="n">
-        <v>451</v>
+        <v>380</v>
       </c>
       <c r="H10" t="n">
-        <v>7.78</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="11">
@@ -812,25 +803,25 @@
         <v>17</v>
       </c>
       <c r="B11" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>0.015402</v>
+        <v>0.015279</v>
       </c>
       <c r="D11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2075</v>
+        <v>0.1961</v>
       </c>
       <c r="G11" t="n">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="H11" t="n">
-        <v>12.44</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="12">
@@ -838,25 +829,25 @@
         <v>18</v>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>0.010462</v>
+        <v>0.010186</v>
       </c>
       <c r="D12" t="n">
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" t="n">
-        <v>0.25</v>
+        <v>0.2059</v>
       </c>
       <c r="G12" t="n">
-        <v>180</v>
+        <v>387</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="13">
@@ -864,25 +855,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C13" t="n">
-        <v>0.010171</v>
+        <v>0.009886</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2</v>
+        <v>0.6061</v>
       </c>
       <c r="G13" t="n">
-        <v>407</v>
+        <v>683</v>
       </c>
       <c r="H13" t="n">
-        <v>11.63</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="14">
@@ -890,25 +881,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C14" t="n">
-        <v>0.009881</v>
+        <v>0.008688</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1471</v>
+        <v>0.1379</v>
       </c>
       <c r="G14" t="n">
-        <v>1340</v>
+        <v>1312</v>
       </c>
       <c r="H14" t="n">
-        <v>39.41</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="15">
@@ -916,25 +907,25 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>0.00959</v>
+        <v>0.008388</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5758</v>
+        <v>0.2857</v>
       </c>
       <c r="G15" t="n">
-        <v>683</v>
+        <v>132</v>
       </c>
       <c r="H15" t="n">
-        <v>20.09</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="16">
@@ -942,25 +933,25 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" t="n">
-        <v>0.008137</v>
+        <v>0.008089</v>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
         <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4286</v>
+        <v>0.4444</v>
       </c>
       <c r="G16" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H16" t="n">
-        <v>8.86</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="17">
@@ -971,7 +962,7 @@
         <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>0.006684</v>
+        <v>0.00689</v>
       </c>
       <c r="D17" t="n">
         <v>16</v>
@@ -994,25 +985,25 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>0.006684</v>
+        <v>0.006291</v>
       </c>
       <c r="D18" t="n">
         <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5217</v>
+        <v>0.4762</v>
       </c>
       <c r="G18" t="n">
-        <v>124</v>
+        <v>559</v>
       </c>
       <c r="H18" t="n">
-        <v>5.39</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="19">
@@ -1020,25 +1011,25 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>0.006393</v>
+        <v>0.006291</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4545</v>
+        <v>0.4762</v>
       </c>
       <c r="G19" t="n">
-        <v>559</v>
+        <v>39</v>
       </c>
       <c r="H19" t="n">
-        <v>25.41</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="20">
@@ -1046,25 +1037,25 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>0.006393</v>
+        <v>0.005992</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4545</v>
+        <v>0.55</v>
       </c>
       <c r="G20" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="H20" t="n">
-        <v>1.82</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="21">
@@ -1072,25 +1063,25 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>0.005522</v>
+        <v>0.005392</v>
       </c>
       <c r="D21" t="n">
         <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2632</v>
+        <v>0.2222</v>
       </c>
       <c r="G21" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="H21" t="n">
-        <v>5.05</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="22">
@@ -1098,25 +1089,25 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" t="n">
-        <v>0.005231</v>
+        <v>0.005093</v>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2222</v>
+        <v>0.0588</v>
       </c>
       <c r="G22" t="n">
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="H22" t="n">
-        <v>6.17</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="23">
@@ -1124,25 +1115,25 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00494</v>
+        <v>0.004793</v>
       </c>
       <c r="D23" t="n">
         <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2941</v>
+        <v>0.25</v>
       </c>
       <c r="G23" t="n">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="H23" t="n">
-        <v>7.29</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="24">
@@ -1150,25 +1141,25 @@
         <v>30</v>
       </c>
       <c r="B24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00494</v>
+        <v>0.004793</v>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0588</v>
+        <v>0.3125</v>
       </c>
       <c r="G24" t="n">
-        <v>183</v>
+        <v>94</v>
       </c>
       <c r="H24" t="n">
-        <v>10.76</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="25">
@@ -1179,7 +1170,7 @@
         <v>16</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00465</v>
+        <v>0.004793</v>
       </c>
       <c r="D25" t="n">
         <v>12</v>
@@ -1202,25 +1193,25 @@
         <v>32</v>
       </c>
       <c r="B26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" t="n">
-        <v>0.004359</v>
+        <v>0.004194</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2667</v>
+        <v>0.2857</v>
       </c>
       <c r="G26" t="n">
         <v>228</v>
       </c>
       <c r="H26" t="n">
-        <v>15.2</v>
+        <v>16.29</v>
       </c>
     </row>
     <row r="27">
@@ -1231,7 +1222,7 @@
         <v>13</v>
       </c>
       <c r="C27" t="n">
-        <v>0.003778</v>
+        <v>0.003895</v>
       </c>
       <c r="D27" t="n">
         <v>11</v>
@@ -1257,7 +1248,7 @@
         <v>12</v>
       </c>
       <c r="C28" t="n">
-        <v>0.003487</v>
+        <v>0.003595</v>
       </c>
       <c r="D28" t="n">
         <v>11</v>
@@ -1280,25 +1271,25 @@
         <v>35</v>
       </c>
       <c r="B29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C29" t="n">
-        <v>0.003197</v>
+        <v>0.002696</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
         <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2727</v>
+        <v>0.3333</v>
       </c>
       <c r="G29" t="n">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="H29" t="n">
-        <v>10.09</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="30">
@@ -1306,25 +1297,25 @@
         <v>36</v>
       </c>
       <c r="B30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>0.002906</v>
+        <v>0.002696</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2</v>
+        <v>0.4444</v>
       </c>
       <c r="G30" t="n">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="H30" t="n">
-        <v>17.8</v>
+        <v>15.56</v>
       </c>
     </row>
     <row r="31">
@@ -1332,25 +1323,25 @@
         <v>37</v>
       </c>
       <c r="B31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" t="n">
-        <v>0.002616</v>
+        <v>0.002397</v>
       </c>
       <c r="D31" t="n">
         <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2222</v>
+        <v>0.125</v>
       </c>
       <c r="G31" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H31" t="n">
-        <v>12.89</v>
+        <v>14.62</v>
       </c>
     </row>
     <row r="32">
@@ -1358,25 +1349,25 @@
         <v>38</v>
       </c>
       <c r="B32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C32" t="n">
-        <v>0.002616</v>
+        <v>0.002397</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4444</v>
+        <v>0.25</v>
       </c>
       <c r="G32" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="H32" t="n">
-        <v>15.56</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="33">
@@ -1384,25 +1375,25 @@
         <v>39</v>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002325</v>
+        <v>0.002097</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
-        <v>0.25</v>
+        <v>0.5714</v>
       </c>
       <c r="G33" t="n">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="H33" t="n">
-        <v>8.38</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="34">
@@ -1410,25 +1401,25 @@
         <v>40</v>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>0.002034</v>
+        <v>0.001797</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5714</v>
+        <v>0.1667</v>
       </c>
       <c r="G34" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="H34" t="n">
-        <v>2.14</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="35">
@@ -1436,25 +1427,25 @@
         <v>41</v>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001744</v>
+        <v>0.001498</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H35" t="n">
-        <v>3.33</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="36">
@@ -1462,25 +1453,25 @@
         <v>42</v>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001744</v>
+        <v>0.001498</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1667</v>
+        <v>0.2</v>
       </c>
       <c r="G36" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H36" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1491,22 +1482,22 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.001453</v>
+        <v>0.001498</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G37" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
-        <v>7.8</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="38">
@@ -1514,25 +1505,25 @@
         <v>44</v>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>0.001453</v>
+        <v>0.001198</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G38" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="39">
@@ -1540,25 +1531,25 @@
         <v>45</v>
       </c>
       <c r="B39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>0.001453</v>
+        <v>0.001198</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H39" t="n">
-        <v>10.8</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="40">
@@ -1566,25 +1557,25 @@
         <v>46</v>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>0.001453</v>
+        <v>0.001198</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="41">
@@ -1592,25 +1583,25 @@
         <v>47</v>
       </c>
       <c r="B41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>0.001453</v>
+        <v>0.001198</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G41" t="n">
         <v>48</v>
       </c>
       <c r="H41" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
@@ -1621,7 +1612,7 @@
         <v>3</v>
       </c>
       <c r="C42" t="n">
-        <v>0.000872</v>
+        <v>0.000899</v>
       </c>
       <c r="D42" t="n">
         <v>2</v>
@@ -1633,10 +1624,10 @@
         <v>0.3333</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H42" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1647,7 +1638,7 @@
         <v>3</v>
       </c>
       <c r="C43" t="n">
-        <v>0.000872</v>
+        <v>0.000899</v>
       </c>
       <c r="D43" t="n">
         <v>2</v>
@@ -1659,10 +1650,10 @@
         <v>0.3333</v>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="44">
@@ -1673,7 +1664,7 @@
         <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>0.000872</v>
+        <v>0.000899</v>
       </c>
       <c r="D44" t="n">
         <v>2</v>
@@ -1685,10 +1676,10 @@
         <v>0.3333</v>
       </c>
       <c r="G44" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H44" t="n">
-        <v>4.33</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="45">
@@ -1696,25 +1687,25 @@
         <v>51</v>
       </c>
       <c r="B45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>0.000872</v>
+        <v>0.000599</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
       <c r="G45" t="n">
         <v>4</v>
       </c>
       <c r="H45" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1725,7 +1716,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>0.000581</v>
+        <v>0.000599</v>
       </c>
       <c r="D46" t="n">
         <v>2</v>
@@ -1751,7 +1742,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>0.000581</v>
+        <v>0.000599</v>
       </c>
       <c r="D47" t="n">
         <v>2</v>
@@ -1777,7 +1768,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>0.000581</v>
+        <v>0.000599</v>
       </c>
       <c r="D48" t="n">
         <v>2</v>
@@ -1803,7 +1794,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>0.000581</v>
+        <v>0.000599</v>
       </c>
       <c r="D49" t="n">
         <v>1</v>
@@ -1829,7 +1820,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>0.000581</v>
+        <v>0.000599</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -1852,25 +1843,25 @@
         <v>57</v>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0.000581</v>
+        <v>0.0003</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1881,16 +1872,16 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.000291</v>
+        <v>0.0003</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1907,16 +1898,16 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0.000291</v>
+        <v>0.0003</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1933,22 +1924,22 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0.000291</v>
+        <v>0.0003</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55">
@@ -1959,7 +1950,7 @@
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>0.000291</v>
+        <v>0.0003</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
@@ -1985,22 +1976,22 @@
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>0.000291</v>
+        <v>0.0003</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2011,7 +2002,7 @@
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>0.000291</v>
+        <v>0.0003</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
@@ -2023,10 +2014,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -2037,22 +2028,22 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>0.000291</v>
+        <v>0.0003</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -2063,100 +2054,22 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.000291</v>
+        <v>0.0003</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>66</v>
-      </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.000291</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="n">
-        <v>23</v>
-      </c>
-      <c r="H60" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>67</v>
-      </c>
-      <c r="B61" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0.000291</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="n">
-        <v>8</v>
-      </c>
-      <c r="H61" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.000291</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="n">
-        <v>2</v>
-      </c>
-      <c r="H62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/files/Countries_Prod_TC.xlsx
+++ b/files/Countries_Prod_TC.xlsx
@@ -74,42 +74,42 @@
     <t xml:space="preserve">New Zealand</t>
   </si>
   <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
     <t xml:space="preserve">Germany</t>
   </si>
   <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
     <t xml:space="preserve">South Korea</t>
   </si>
   <si>
     <t xml:space="preserve">Ireland</t>
   </si>
   <si>
+    <t xml:space="preserve">Iran</t>
+  </si>
+  <si>
     <t xml:space="preserve">Belgium</t>
   </si>
   <si>
-    <t xml:space="preserve">Iran</t>
-  </si>
-  <si>
     <t xml:space="preserve">Norway</t>
   </si>
   <si>
+    <t xml:space="preserve">Georgia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Indonesia</t>
   </si>
   <si>
-    <t xml:space="preserve">Georgia</t>
+    <t xml:space="preserve">India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saudi Arabia</t>
   </si>
   <si>
     <t xml:space="preserve">France</t>
   </si>
   <si>
-    <t xml:space="preserve">India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saudi Arabia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Israel</t>
   </si>
   <si>
@@ -119,30 +119,30 @@
     <t xml:space="preserve">Cyprus</t>
   </si>
   <si>
+    <t xml:space="preserve">Singapore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greece</t>
+  </si>
+  <si>
     <t xml:space="preserve">Malaysia</t>
   </si>
   <si>
-    <t xml:space="preserve">Singapore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greece</t>
-  </si>
-  <si>
     <t xml:space="preserve">South Africa</t>
   </si>
   <si>
+    <t xml:space="preserve">Switzerland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czech Republic</t>
+  </si>
+  <si>
     <t xml:space="preserve">Denmark</t>
   </si>
   <si>
-    <t xml:space="preserve">Switzerland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czech Republic</t>
-  </si>
-  <si>
     <t xml:space="preserve">Poland</t>
   </si>
   <si>
@@ -152,61 +152,61 @@
     <t xml:space="preserve">Finland</t>
   </si>
   <si>
+    <t xml:space="preserve">Lithuania</t>
+  </si>
+  <si>
     <t xml:space="preserve">Portugal</t>
   </si>
   <si>
     <t xml:space="preserve">Romania</t>
   </si>
   <si>
-    <t xml:space="preserve">Lithuania</t>
+    <t xml:space="preserve">UAE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iceland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuwait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pakistan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qatar</t>
   </si>
   <si>
     <t xml:space="preserve">Thailand</t>
   </si>
   <si>
-    <t xml:space="preserve">UAE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iceland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kuwait</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pakistan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qatar</t>
+    <t xml:space="preserve">Ecuador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egypt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazakhstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morocco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serbia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sri Lanka</t>
   </si>
   <si>
     <t xml:space="preserve">Tanzania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecuador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egypt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kazakhstan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morocco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serbia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sri Lanka</t>
   </si>
   <si>
     <t xml:space="preserve">Tunisia</t>
@@ -569,25 +569,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>2089</v>
+        <v>2082</v>
       </c>
       <c r="C2" t="n">
-        <v>0.625824</v>
+        <v>0.630145</v>
       </c>
       <c r="D2" t="n">
-        <v>1976</v>
+        <v>1969</v>
       </c>
       <c r="E2" t="n">
         <v>113</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0541</v>
+        <v>0.0543</v>
       </c>
       <c r="G2" t="n">
-        <v>51828</v>
+        <v>51499</v>
       </c>
       <c r="H2" t="n">
-        <v>24.75</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="3">
@@ -598,7 +598,7 @@
         <v>130</v>
       </c>
       <c r="C3" t="n">
-        <v>0.038945</v>
+        <v>0.039346</v>
       </c>
       <c r="D3" t="n">
         <v>109</v>
@@ -621,25 +621,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C4" t="n">
-        <v>0.036848</v>
+        <v>0.035109</v>
       </c>
       <c r="D4" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2195</v>
+        <v>0.2069</v>
       </c>
       <c r="G4" t="n">
-        <v>1295</v>
+        <v>1235</v>
       </c>
       <c r="H4" t="n">
-        <v>10.53</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="5">
@@ -647,25 +647,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C5" t="n">
-        <v>0.033553</v>
+        <v>0.033293</v>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E5" t="n">
         <v>30</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2679</v>
+        <v>0.2727</v>
       </c>
       <c r="G5" t="n">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="H5" t="n">
-        <v>18.13</v>
+        <v>18.45</v>
       </c>
     </row>
     <row r="6">
@@ -673,25 +673,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" t="n">
-        <v>0.031456</v>
+        <v>0.031477</v>
       </c>
       <c r="D6" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" t="n">
         <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2762</v>
+        <v>0.2788</v>
       </c>
       <c r="G6" t="n">
-        <v>2389</v>
+        <v>2379</v>
       </c>
       <c r="H6" t="n">
-        <v>22.75</v>
+        <v>22.88</v>
       </c>
     </row>
     <row r="7">
@@ -702,7 +702,7 @@
         <v>79</v>
       </c>
       <c r="C7" t="n">
-        <v>0.023667</v>
+        <v>0.02391</v>
       </c>
       <c r="D7" t="n">
         <v>44</v>
@@ -728,7 +728,7 @@
         <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>0.020371</v>
+        <v>0.020581</v>
       </c>
       <c r="D8" t="n">
         <v>63</v>
@@ -751,25 +751,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>0.018874</v>
+        <v>0.018765</v>
       </c>
       <c r="D9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9" t="n">
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>0.381</v>
+        <v>0.3871</v>
       </c>
       <c r="G9" t="n">
         <v>758</v>
       </c>
       <c r="H9" t="n">
-        <v>12.03</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="10">
@@ -780,7 +780,7 @@
         <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>0.015578</v>
+        <v>0.015738</v>
       </c>
       <c r="D10" t="n">
         <v>44</v>
@@ -806,7 +806,7 @@
         <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>0.015279</v>
+        <v>0.015436</v>
       </c>
       <c r="D11" t="n">
         <v>41</v>
@@ -832,7 +832,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>0.010186</v>
+        <v>0.010291</v>
       </c>
       <c r="D12" t="n">
         <v>27</v>
@@ -858,7 +858,7 @@
         <v>33</v>
       </c>
       <c r="C13" t="n">
-        <v>0.009886</v>
+        <v>0.009988</v>
       </c>
       <c r="D13" t="n">
         <v>13</v>
@@ -881,25 +881,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C14" t="n">
-        <v>0.008688</v>
+        <v>0.008172</v>
       </c>
       <c r="D14" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1379</v>
+        <v>0.2963</v>
       </c>
       <c r="G14" t="n">
-        <v>1312</v>
+        <v>131</v>
       </c>
       <c r="H14" t="n">
-        <v>45.24</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="15">
@@ -907,25 +907,25 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>0.008388</v>
+        <v>0.008172</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2857</v>
+        <v>0.1481</v>
       </c>
       <c r="G15" t="n">
-        <v>132</v>
+        <v>1309</v>
       </c>
       <c r="H15" t="n">
-        <v>4.71</v>
+        <v>48.48</v>
       </c>
     </row>
     <row r="16">
@@ -933,25 +933,25 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" t="n">
-        <v>0.008089</v>
+        <v>0.007869</v>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
         <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4444</v>
+        <v>0.4615</v>
       </c>
       <c r="G16" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H16" t="n">
-        <v>9.07</v>
+        <v>9.38</v>
       </c>
     </row>
     <row r="17">
@@ -962,7 +962,7 @@
         <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00689</v>
+        <v>0.006961</v>
       </c>
       <c r="D17" t="n">
         <v>16</v>
@@ -988,7 +988,7 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>0.006291</v>
+        <v>0.006356</v>
       </c>
       <c r="D18" t="n">
         <v>11</v>
@@ -1000,10 +1000,10 @@
         <v>0.4762</v>
       </c>
       <c r="G18" t="n">
-        <v>559</v>
+        <v>39</v>
       </c>
       <c r="H18" t="n">
-        <v>26.62</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="19">
@@ -1011,25 +1011,25 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
-        <v>0.006291</v>
+        <v>0.006053</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4762</v>
+        <v>0.5</v>
       </c>
       <c r="G19" t="n">
-        <v>39</v>
+        <v>558</v>
       </c>
       <c r="H19" t="n">
-        <v>1.86</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="20">
@@ -1040,7 +1040,7 @@
         <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>0.005992</v>
+        <v>0.006053</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
@@ -1063,25 +1063,25 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>0.005392</v>
+        <v>0.005145</v>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2222</v>
+        <v>0.0588</v>
       </c>
       <c r="G21" t="n">
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="H21" t="n">
-        <v>6.17</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="22">
@@ -1092,22 +1092,22 @@
         <v>17</v>
       </c>
       <c r="C22" t="n">
-        <v>0.005093</v>
+        <v>0.005145</v>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0588</v>
+        <v>0.1765</v>
       </c>
       <c r="G22" t="n">
-        <v>183</v>
+        <v>110</v>
       </c>
       <c r="H22" t="n">
-        <v>10.76</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="23">
@@ -1118,22 +1118,22 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>0.004793</v>
+        <v>0.004843</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="G23" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="H23" t="n">
-        <v>6.38</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="24">
@@ -1144,22 +1144,22 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>0.004793</v>
+        <v>0.004843</v>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3125</v>
+        <v>0.25</v>
       </c>
       <c r="G24" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H24" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="25">
@@ -1167,25 +1167,25 @@
         <v>31</v>
       </c>
       <c r="B25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C25" t="n">
-        <v>0.004793</v>
+        <v>0.00454</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
         <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>0.25</v>
+        <v>0.2667</v>
       </c>
       <c r="G25" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H25" t="n">
-        <v>5.56</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="26">
@@ -1196,7 +1196,7 @@
         <v>14</v>
       </c>
       <c r="C26" t="n">
-        <v>0.004194</v>
+        <v>0.004237</v>
       </c>
       <c r="D26" t="n">
         <v>10</v>
@@ -1222,7 +1222,7 @@
         <v>13</v>
       </c>
       <c r="C27" t="n">
-        <v>0.003895</v>
+        <v>0.003935</v>
       </c>
       <c r="D27" t="n">
         <v>11</v>
@@ -1248,7 +1248,7 @@
         <v>12</v>
       </c>
       <c r="C28" t="n">
-        <v>0.003595</v>
+        <v>0.003632</v>
       </c>
       <c r="D28" t="n">
         <v>11</v>
@@ -1274,22 +1274,22 @@
         <v>9</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002696</v>
+        <v>0.002724</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3333</v>
+        <v>0.4444</v>
       </c>
       <c r="G29" t="n">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="H29" t="n">
-        <v>10.44</v>
+        <v>15.56</v>
       </c>
     </row>
     <row r="30">
@@ -1297,25 +1297,25 @@
         <v>36</v>
       </c>
       <c r="B30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" t="n">
-        <v>0.002696</v>
+        <v>0.002421</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4444</v>
+        <v>0.125</v>
       </c>
       <c r="G30" t="n">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="H30" t="n">
-        <v>15.56</v>
+        <v>14.62</v>
       </c>
     </row>
     <row r="31">
@@ -1326,22 +1326,22 @@
         <v>8</v>
       </c>
       <c r="C31" t="n">
-        <v>0.002397</v>
+        <v>0.002421</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.125</v>
+        <v>0.375</v>
       </c>
       <c r="G31" t="n">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="H31" t="n">
-        <v>14.62</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="32">
@@ -1349,25 +1349,25 @@
         <v>38</v>
       </c>
       <c r="B32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32" t="n">
-        <v>0.002397</v>
+        <v>0.002119</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>0.25</v>
+        <v>0.2857</v>
       </c>
       <c r="G32" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H32" t="n">
-        <v>16.62</v>
+        <v>18.86</v>
       </c>
     </row>
     <row r="33">
@@ -1375,25 +1375,25 @@
         <v>39</v>
       </c>
       <c r="B33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002097</v>
+        <v>0.001816</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5714</v>
+        <v>0.1667</v>
       </c>
       <c r="G33" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="H33" t="n">
-        <v>2.14</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="34">
@@ -1401,25 +1401,25 @@
         <v>40</v>
       </c>
       <c r="B34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001797</v>
+        <v>0.001513</v>
       </c>
       <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
         <v>5</v>
       </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
       <c r="F34" t="n">
-        <v>0.1667</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="H34" t="n">
-        <v>8.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="35">
@@ -1430,22 +1430,22 @@
         <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001498</v>
+        <v>0.001513</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="G35" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H35" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1456,22 +1456,22 @@
         <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001498</v>
+        <v>0.001513</v>
       </c>
       <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
         <v>4</v>
       </c>
-      <c r="E36" t="n">
-        <v>1</v>
-      </c>
       <c r="F36" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G36" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="37">
@@ -1482,7 +1482,7 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.001498</v>
+        <v>0.001513</v>
       </c>
       <c r="D37" t="n">
         <v>4</v>
@@ -1508,7 +1508,7 @@
         <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>0.001198</v>
+        <v>0.001211</v>
       </c>
       <c r="D38" t="n">
         <v>2</v>
@@ -1531,25 +1531,25 @@
         <v>45</v>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>0.001198</v>
+        <v>0.000908</v>
       </c>
       <c r="D39" t="n">
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
       <c r="G39" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="H39" t="n">
-        <v>13.25</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="40">
@@ -1557,25 +1557,25 @@
         <v>46</v>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>0.001198</v>
+        <v>0.000908</v>
       </c>
       <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="G40" t="n">
         <v>3</v>
       </c>
-      <c r="E40" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G40" t="n">
-        <v>7</v>
-      </c>
       <c r="H40" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1583,25 +1583,25 @@
         <v>47</v>
       </c>
       <c r="B41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C41" t="n">
-        <v>0.001198</v>
+        <v>0.000908</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0.25</v>
+        <v>0.3333</v>
       </c>
       <c r="G41" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="H41" t="n">
-        <v>12</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="42">
@@ -1612,7 +1612,7 @@
         <v>3</v>
       </c>
       <c r="C42" t="n">
-        <v>0.000899</v>
+        <v>0.000908</v>
       </c>
       <c r="D42" t="n">
         <v>2</v>
@@ -1624,10 +1624,10 @@
         <v>0.3333</v>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -1638,7 +1638,7 @@
         <v>3</v>
       </c>
       <c r="C43" t="n">
-        <v>0.000899</v>
+        <v>0.000908</v>
       </c>
       <c r="D43" t="n">
         <v>2</v>
@@ -1650,10 +1650,10 @@
         <v>0.3333</v>
       </c>
       <c r="G43" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H43" t="n">
-        <v>4.33</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="44">
@@ -1661,25 +1661,25 @@
         <v>50</v>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>0.000899</v>
+        <v>0.000605</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
       <c r="G44" t="n">
         <v>4</v>
       </c>
       <c r="H44" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1690,22 +1690,22 @@
         <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>0.000599</v>
+        <v>0.000605</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
@@ -1716,7 +1716,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>0.000599</v>
+        <v>0.000605</v>
       </c>
       <c r="D46" t="n">
         <v>2</v>
@@ -1728,10 +1728,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
-        <v>18</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="47">
@@ -1742,7 +1742,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>0.000599</v>
+        <v>0.000605</v>
       </c>
       <c r="D47" t="n">
         <v>2</v>
@@ -1754,10 +1754,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -1768,22 +1768,22 @@
         <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>0.000599</v>
+        <v>0.000605</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="49">
@@ -1794,7 +1794,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>0.000599</v>
+        <v>0.000605</v>
       </c>
       <c r="D49" t="n">
         <v>1</v>
@@ -1806,10 +1806,10 @@
         <v>0.5</v>
       </c>
       <c r="G49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H49" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
@@ -1817,25 +1817,25 @@
         <v>56</v>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.000599</v>
+        <v>0.000303</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1846,16 +1846,16 @@
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0003</v>
+        <v>0.000303</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1872,16 +1872,16 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0003</v>
+        <v>0.000303</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1898,22 +1898,22 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0003</v>
+        <v>0.000303</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54">
@@ -1924,22 +1924,22 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0003</v>
+        <v>0.000303</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1950,7 +1950,7 @@
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0003</v>
+        <v>0.000303</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
@@ -1976,7 +1976,7 @@
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0003</v>
+        <v>0.000303</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
@@ -1988,10 +1988,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -2002,22 +2002,22 @@
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0003</v>
+        <v>0.000303</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
@@ -2028,7 +2028,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0003</v>
+        <v>0.000303</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2040,10 +2040,10 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H58" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -2054,7 +2054,7 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0003</v>
+        <v>0.000303</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>

--- a/files/Countries_Prod_TC.xlsx
+++ b/files/Countries_Prod_TC.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -62,12 +62,12 @@
     <t xml:space="preserve">Spain</t>
   </si>
   <si>
+    <t xml:space="preserve">Netherlands</t>
+  </si>
+  <si>
     <t xml:space="preserve">Japan</t>
   </si>
   <si>
-    <t xml:space="preserve">Netherlands</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sweden</t>
   </si>
   <si>
@@ -89,49 +89,55 @@
     <t xml:space="preserve">Iran</t>
   </si>
   <si>
+    <t xml:space="preserve">Norway</t>
+  </si>
+  <si>
     <t xml:space="preserve">Belgium</t>
   </si>
   <si>
-    <t xml:space="preserve">Norway</t>
+    <t xml:space="preserve">Saudi Arabia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indonesia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mexico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyprus</t>
   </si>
   <si>
     <t xml:space="preserve">Georgia</t>
   </si>
   <si>
-    <t xml:space="preserve">Indonesia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saudi Arabia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mexico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyprus</t>
+    <t xml:space="preserve">Malaysia</t>
   </si>
   <si>
     <t xml:space="preserve">Singapore</t>
   </si>
   <si>
+    <t xml:space="preserve">South Africa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switzerland</t>
+  </si>
+  <si>
     <t xml:space="preserve">Greece</t>
   </si>
   <si>
-    <t xml:space="preserve">Malaysia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Africa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switzerland</t>
+    <t xml:space="preserve">Denmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colombia</t>
   </si>
   <si>
     <t xml:space="preserve">Austria</t>
@@ -140,22 +146,22 @@
     <t xml:space="preserve">Czech Republic</t>
   </si>
   <si>
-    <t xml:space="preserve">Denmark</t>
-  </si>
-  <si>
     <t xml:space="preserve">Poland</t>
   </si>
   <si>
-    <t xml:space="preserve">Colombia</t>
+    <t xml:space="preserve">Portugal</t>
   </si>
   <si>
     <t xml:space="preserve">Finland</t>
   </si>
   <si>
+    <t xml:space="preserve">Kuwait</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lithuania</t>
   </si>
   <si>
-    <t xml:space="preserve">Portugal</t>
+    <t xml:space="preserve">Qatar</t>
   </si>
   <si>
     <t xml:space="preserve">Romania</t>
@@ -170,24 +176,24 @@
     <t xml:space="preserve">Iceland</t>
   </si>
   <si>
-    <t xml:space="preserve">Kuwait</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pakistan</t>
   </si>
   <si>
-    <t xml:space="preserve">Qatar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Thailand</t>
   </si>
   <si>
+    <t xml:space="preserve">Tunisia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ecuador</t>
   </si>
   <si>
     <t xml:space="preserve">Egypt</t>
   </si>
   <si>
+    <t xml:space="preserve">Jordan</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kazakhstan</t>
   </si>
   <si>
@@ -207,9 +213,6 @@
   </si>
   <si>
     <t xml:space="preserve">Tanzania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tunisia</t>
   </si>
 </sst>
 </file>
@@ -569,25 +572,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>2082</v>
+        <v>2105</v>
       </c>
       <c r="C2" t="n">
-        <v>0.630145</v>
+        <v>0.625743</v>
       </c>
       <c r="D2" t="n">
-        <v>1969</v>
+        <v>2095</v>
       </c>
       <c r="E2" t="n">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0543</v>
+        <v>0.00475</v>
       </c>
       <c r="G2" t="n">
-        <v>51499</v>
+        <v>52605</v>
       </c>
       <c r="H2" t="n">
-        <v>24.68</v>
+        <v>24.81</v>
       </c>
     </row>
     <row r="3">
@@ -598,22 +601,22 @@
         <v>130</v>
       </c>
       <c r="C3" t="n">
-        <v>0.039346</v>
+        <v>0.038644</v>
       </c>
       <c r="D3" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1615</v>
+        <v>0.00769</v>
       </c>
       <c r="G3" t="n">
-        <v>2093</v>
+        <v>2164</v>
       </c>
       <c r="H3" t="n">
-        <v>16.1</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="4">
@@ -621,25 +624,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C4" t="n">
-        <v>0.035109</v>
+        <v>0.03478</v>
       </c>
       <c r="D4" t="n">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>-2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2069</v>
+        <v>-0.01709</v>
       </c>
       <c r="G4" t="n">
-        <v>1235</v>
+        <v>1343</v>
       </c>
       <c r="H4" t="n">
-        <v>10.65</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="5">
@@ -650,22 +653,22 @@
         <v>110</v>
       </c>
       <c r="C5" t="n">
-        <v>0.033293</v>
+        <v>0.032699</v>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2727</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2029</v>
+        <v>2067</v>
       </c>
       <c r="H5" t="n">
-        <v>18.45</v>
+        <v>18.79</v>
       </c>
     </row>
     <row r="6">
@@ -673,25 +676,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" t="n">
-        <v>0.031477</v>
+        <v>0.031213</v>
       </c>
       <c r="D6" t="n">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E6" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2788</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2379</v>
+        <v>2370</v>
       </c>
       <c r="H6" t="n">
-        <v>22.88</v>
+        <v>22.57</v>
       </c>
     </row>
     <row r="7">
@@ -699,25 +702,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02391</v>
+        <v>0.024078</v>
       </c>
       <c r="D7" t="n">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="E7" t="n">
-        <v>35</v>
+        <v>-2</v>
       </c>
       <c r="F7" t="n">
-        <v>0.443</v>
+        <v>-0.02469</v>
       </c>
       <c r="G7" t="n">
-        <v>897</v>
+        <v>916</v>
       </c>
       <c r="H7" t="n">
-        <v>11.35</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="8">
@@ -725,25 +728,25 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
+        <v>67</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.019917</v>
+      </c>
+      <c r="D8" t="n">
         <v>68</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.020581</v>
-      </c>
-      <c r="D8" t="n">
-        <v>63</v>
-      </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0735</v>
+        <v>-0.01493</v>
       </c>
       <c r="G8" t="n">
-        <v>665</v>
+        <v>711</v>
       </c>
       <c r="H8" t="n">
-        <v>9.64</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +757,22 @@
         <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>0.018765</v>
+        <v>0.01843</v>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3871</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>758</v>
+        <v>780</v>
       </c>
       <c r="H9" t="n">
-        <v>12.23</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="10">
@@ -777,25 +780,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>0.015738</v>
+        <v>0.016647</v>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1538</v>
+        <v>-0.01786</v>
       </c>
       <c r="G10" t="n">
-        <v>380</v>
+        <v>711</v>
       </c>
       <c r="H10" t="n">
-        <v>7.31</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="11">
@@ -803,25 +806,25 @@
         <v>17</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11" t="n">
-        <v>0.015436</v>
+        <v>0.015458</v>
       </c>
       <c r="D11" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1961</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>677</v>
+        <v>396</v>
       </c>
       <c r="H11" t="n">
-        <v>13.02</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="12">
@@ -829,25 +832,25 @@
         <v>18</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n">
-        <v>0.010291</v>
+        <v>0.010999</v>
       </c>
       <c r="D12" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2059</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>387</v>
+        <v>415</v>
       </c>
       <c r="H12" t="n">
-        <v>11.38</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="13">
@@ -855,25 +858,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="n">
+        <v>32</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.009512</v>
+      </c>
+      <c r="D13" t="n">
         <v>33</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.009988</v>
-      </c>
-      <c r="D13" t="n">
-        <v>13</v>
-      </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>-1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6061</v>
+        <v>-0.03125</v>
       </c>
       <c r="G13" t="n">
-        <v>683</v>
+        <v>712</v>
       </c>
       <c r="H13" t="n">
-        <v>20.7</v>
+        <v>21.58</v>
       </c>
     </row>
     <row r="14">
@@ -881,25 +884,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C14" t="n">
-        <v>0.008172</v>
+        <v>0.008918</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2963</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H14" t="n">
-        <v>4.85</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="15">
@@ -907,25 +910,25 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C15" t="n">
-        <v>0.008172</v>
+        <v>0.008918</v>
       </c>
       <c r="D15" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1481</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1309</v>
+        <v>1338</v>
       </c>
       <c r="H15" t="n">
-        <v>48.48</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="16">
@@ -933,25 +936,25 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C16" t="n">
-        <v>0.007869</v>
+        <v>0.008323</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4615</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="H16" t="n">
-        <v>9.38</v>
+        <v>9.14</v>
       </c>
     </row>
     <row r="17">
@@ -959,25 +962,25 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>0.006961</v>
+        <v>0.007134</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3043</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="H17" t="n">
-        <v>17.83</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="18">
@@ -985,25 +988,25 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
-        <v>0.006356</v>
+        <v>0.00654</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4762</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="H18" t="n">
-        <v>1.86</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="19">
@@ -1011,25 +1014,25 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>0.006053</v>
+        <v>0.00654</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>558</v>
+        <v>122</v>
       </c>
       <c r="H19" t="n">
-        <v>27.9</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="20">
@@ -1040,22 +1043,22 @@
         <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>0.006053</v>
+        <v>0.005945</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>110</v>
+        <v>477</v>
       </c>
       <c r="H20" t="n">
-        <v>5.5</v>
+        <v>23.85</v>
       </c>
     </row>
     <row r="21">
@@ -1063,25 +1066,25 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>0.005145</v>
+        <v>0.005351</v>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>183</v>
+        <v>102</v>
       </c>
       <c r="H21" t="n">
-        <v>10.76</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="22">
@@ -1092,22 +1095,22 @@
         <v>17</v>
       </c>
       <c r="C22" t="n">
-        <v>0.005145</v>
+        <v>0.005054</v>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1765</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="H22" t="n">
-        <v>6.47</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="23">
@@ -1115,25 +1118,25 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C23" t="n">
-        <v>0.004843</v>
+        <v>0.005054</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3125</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="H23" t="n">
-        <v>5.88</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="24">
@@ -1144,22 +1147,22 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>0.004843</v>
+        <v>0.004756</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="F24" t="n">
-        <v>0.25</v>
+        <v>-0.0625</v>
       </c>
       <c r="G24" t="n">
-        <v>89</v>
+        <v>230</v>
       </c>
       <c r="H24" t="n">
-        <v>5.56</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="25">
@@ -1167,25 +1170,25 @@
         <v>31</v>
       </c>
       <c r="B25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00454</v>
+        <v>0.004162</v>
       </c>
       <c r="D25" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2667</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H25" t="n">
-        <v>6.53</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="26">
@@ -1193,25 +1196,25 @@
         <v>32</v>
       </c>
       <c r="B26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26" t="n">
-        <v>0.004237</v>
+        <v>0.003864</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2857</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="H26" t="n">
-        <v>16.29</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="27">
@@ -1219,25 +1222,25 @@
         <v>33</v>
       </c>
       <c r="B27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C27" t="n">
-        <v>0.003935</v>
+        <v>0.003567</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1538</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>235</v>
+        <v>30</v>
       </c>
       <c r="H27" t="n">
-        <v>18.08</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="28">
@@ -1248,7 +1251,7 @@
         <v>12</v>
       </c>
       <c r="C28" t="n">
-        <v>0.003632</v>
+        <v>0.003567</v>
       </c>
       <c r="D28" t="n">
         <v>11</v>
@@ -1257,13 +1260,13 @@
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0833</v>
+        <v>0.08333</v>
       </c>
       <c r="G28" t="n">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="H28" t="n">
-        <v>2.33</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="29">
@@ -1271,25 +1274,25 @@
         <v>35</v>
       </c>
       <c r="B29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002724</v>
+        <v>0.002973</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4444</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="H29" t="n">
-        <v>15.56</v>
+        <v>9.8</v>
       </c>
     </row>
     <row r="30">
@@ -1297,25 +1300,25 @@
         <v>36</v>
       </c>
       <c r="B30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>0.002421</v>
+        <v>0.002675</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="H30" t="n">
-        <v>14.62</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="31">
@@ -1323,25 +1326,25 @@
         <v>37</v>
       </c>
       <c r="B31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31" t="n">
-        <v>0.002421</v>
+        <v>0.002675</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="H31" t="n">
-        <v>11.62</v>
+        <v>15.56</v>
       </c>
     </row>
     <row r="32">
@@ -1349,25 +1352,25 @@
         <v>38</v>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C32" t="n">
-        <v>0.002119</v>
+        <v>0.002675</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2857</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="H32" t="n">
-        <v>18.86</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="33">
@@ -1375,25 +1378,25 @@
         <v>39</v>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001816</v>
+        <v>0.002378</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="H33" t="n">
-        <v>8.5</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="34">
@@ -1401,25 +1404,25 @@
         <v>40</v>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001513</v>
+        <v>0.002081</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H34" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="35">
@@ -1427,25 +1430,25 @@
         <v>41</v>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001513</v>
+        <v>0.001784</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -1456,22 +1459,22 @@
         <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001513</v>
+        <v>0.001486</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H36" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="37">
@@ -1482,7 +1485,7 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.001513</v>
+        <v>0.001486</v>
       </c>
       <c r="D37" t="n">
         <v>4</v>
@@ -1494,10 +1497,10 @@
         <v>0.2</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="38">
@@ -1505,25 +1508,25 @@
         <v>44</v>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38" t="n">
-        <v>0.001211</v>
+        <v>0.001486</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="H38" t="n">
-        <v>9.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1531,25 +1534,25 @@
         <v>45</v>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>0.000908</v>
+        <v>0.001189</v>
       </c>
       <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>8</v>
+      </c>
+      <c r="H39" t="n">
         <v>2</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="G39" t="n">
-        <v>41</v>
-      </c>
-      <c r="H39" t="n">
-        <v>13.67</v>
       </c>
     </row>
     <row r="40">
@@ -1560,22 +1563,22 @@
         <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>0.000908</v>
+        <v>0.000892</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>15.67</v>
       </c>
     </row>
     <row r="41">
@@ -1586,22 +1589,22 @@
         <v>3</v>
       </c>
       <c r="C41" t="n">
-        <v>0.000908</v>
+        <v>0.000892</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H41" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="42">
@@ -1612,22 +1615,22 @@
         <v>3</v>
       </c>
       <c r="C42" t="n">
-        <v>0.000908</v>
+        <v>0.000892</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>16</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="43">
@@ -1638,22 +1641,22 @@
         <v>3</v>
       </c>
       <c r="C43" t="n">
-        <v>0.000908</v>
+        <v>0.000892</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H43" t="n">
-        <v>1.33</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="44">
@@ -1661,25 +1664,25 @@
         <v>50</v>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>0.000605</v>
+        <v>0.000892</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
@@ -1687,13 +1690,13 @@
         <v>51</v>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" t="n">
-        <v>0.000605</v>
+        <v>0.000892</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -1702,10 +1705,10 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="H45" t="n">
-        <v>18</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="46">
@@ -1716,7 +1719,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>0.000605</v>
+        <v>0.000595</v>
       </c>
       <c r="D46" t="n">
         <v>2</v>
@@ -1728,10 +1731,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H46" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1742,7 +1745,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>0.000605</v>
+        <v>0.000595</v>
       </c>
       <c r="D47" t="n">
         <v>2</v>
@@ -1754,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
@@ -1768,22 +1771,22 @@
         <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>0.000605</v>
+        <v>0.000595</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -1794,22 +1797,22 @@
         <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>0.000605</v>
+        <v>0.000595</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H49" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="50">
@@ -1817,13 +1820,13 @@
         <v>56</v>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>0.000303</v>
+        <v>0.000595</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -1832,10 +1835,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1846,16 +1849,16 @@
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0.000303</v>
+        <v>0.000297</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1872,7 +1875,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.000303</v>
+        <v>0.000297</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
@@ -1898,22 +1901,22 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0.000303</v>
+        <v>0.000297</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1924,7 +1927,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0.000303</v>
+        <v>0.000297</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
@@ -1950,7 +1953,7 @@
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>0.000303</v>
+        <v>0.000297</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
@@ -1962,10 +1965,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56">
@@ -1976,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>0.000303</v>
+        <v>0.000297</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
@@ -1988,10 +1991,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2002,22 +2005,22 @@
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>0.000303</v>
+        <v>0.000297</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2028,22 +2031,22 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>0.000303</v>
+        <v>0.000297</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2054,22 +2057,48 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.000303</v>
+        <v>0.000297</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H59" t="n">
-        <v>3</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.000297</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>6</v>
+      </c>
+      <c r="H60" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/files/Countries_Prod_TC.xlsx
+++ b/files/Countries_Prod_TC.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -41,27 +41,27 @@
     <t xml:space="preserve">USA</t>
   </si>
   <si>
+    <t xml:space="preserve">China</t>
+  </si>
+  <si>
     <t xml:space="preserve">Canada</t>
   </si>
   <si>
-    <t xml:space="preserve">China</t>
+    <t xml:space="preserve">UK</t>
   </si>
   <si>
     <t xml:space="preserve">Australia</t>
   </si>
   <si>
-    <t xml:space="preserve">UK</t>
-  </si>
-  <si>
     <t xml:space="preserve">Italy</t>
   </si>
   <si>
+    <t xml:space="preserve">Spain</t>
+  </si>
+  <si>
     <t xml:space="preserve">Turkey</t>
   </si>
   <si>
-    <t xml:space="preserve">Spain</t>
-  </si>
-  <si>
     <t xml:space="preserve">Netherlands</t>
   </si>
   <si>
@@ -71,45 +71,45 @@
     <t xml:space="preserve">Sweden</t>
   </si>
   <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
     <t xml:space="preserve">New Zealand</t>
   </si>
   <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany</t>
-  </si>
-  <si>
     <t xml:space="preserve">South Korea</t>
   </si>
   <si>
     <t xml:space="preserve">Ireland</t>
   </si>
   <si>
+    <t xml:space="preserve">Norway</t>
+  </si>
+  <si>
     <t xml:space="preserve">Iran</t>
   </si>
   <si>
-    <t xml:space="preserve">Norway</t>
-  </si>
-  <si>
     <t xml:space="preserve">Belgium</t>
   </si>
   <si>
+    <t xml:space="preserve">India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indonesia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Saudi Arabia</t>
   </si>
   <si>
-    <t xml:space="preserve">India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indonesia</t>
+    <t xml:space="preserve">France</t>
   </si>
   <si>
     <t xml:space="preserve">Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mexico</t>
   </si>
   <si>
@@ -122,15 +122,15 @@
     <t xml:space="preserve">Malaysia</t>
   </si>
   <si>
+    <t xml:space="preserve">Switzerland</t>
+  </si>
+  <si>
     <t xml:space="preserve">Singapore</t>
   </si>
   <si>
     <t xml:space="preserve">South Africa</t>
   </si>
   <si>
-    <t xml:space="preserve">Switzerland</t>
-  </si>
-  <si>
     <t xml:space="preserve">Greece</t>
   </si>
   <si>
@@ -152,6 +152,9 @@
     <t xml:space="preserve">Portugal</t>
   </si>
   <si>
+    <t xml:space="preserve">Romania</t>
+  </si>
+  <si>
     <t xml:space="preserve">Finland</t>
   </si>
   <si>
@@ -164,7 +167,7 @@
     <t xml:space="preserve">Qatar</t>
   </si>
   <si>
-    <t xml:space="preserve">Romania</t>
+    <t xml:space="preserve">Thailand</t>
   </si>
   <si>
     <t xml:space="preserve">UAE</t>
@@ -179,9 +182,6 @@
     <t xml:space="preserve">Pakistan</t>
   </si>
   <si>
-    <t xml:space="preserve">Thailand</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tunisia</t>
   </si>
   <si>
@@ -207,6 +207,9 @@
   </si>
   <si>
     <t xml:space="preserve">Serbia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovakia</t>
   </si>
   <si>
     <t xml:space="preserve">Sri Lanka</t>
@@ -572,25 +575,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>2105</v>
+        <v>2145</v>
       </c>
       <c r="C2" t="n">
-        <v>0.625743</v>
+        <v>0.616202</v>
       </c>
       <c r="D2" t="n">
-        <v>2095</v>
+        <v>2132</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00475</v>
+        <v>0.00606</v>
       </c>
       <c r="G2" t="n">
-        <v>52605</v>
+        <v>53842</v>
       </c>
       <c r="H2" t="n">
-        <v>24.81</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="3">
@@ -598,25 +601,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="C3" t="n">
-        <v>0.038644</v>
+        <v>0.041367</v>
       </c>
       <c r="D3" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00769</v>
+        <v>-0.01389</v>
       </c>
       <c r="G3" t="n">
-        <v>2164</v>
+        <v>1425</v>
       </c>
       <c r="H3" t="n">
-        <v>16.65</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="4">
@@ -624,25 +627,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03478</v>
+        <v>0.038495</v>
       </c>
       <c r="D4" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="E4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01709</v>
+        <v>0.00746</v>
       </c>
       <c r="G4" t="n">
-        <v>1343</v>
+        <v>2367</v>
       </c>
       <c r="H4" t="n">
-        <v>11.29</v>
+        <v>17.66</v>
       </c>
     </row>
     <row r="5">
@@ -650,13 +653,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C5" t="n">
-        <v>0.032699</v>
+        <v>0.031887</v>
       </c>
       <c r="D5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -665,10 +668,10 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2067</v>
+        <v>2532</v>
       </c>
       <c r="H5" t="n">
-        <v>18.79</v>
+        <v>22.81</v>
       </c>
     </row>
     <row r="6">
@@ -676,13 +679,13 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C6" t="n">
-        <v>0.031213</v>
+        <v>0.031026</v>
       </c>
       <c r="D6" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -691,10 +694,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2370</v>
+        <v>1886</v>
       </c>
       <c r="H6" t="n">
-        <v>22.57</v>
+        <v>17.46</v>
       </c>
     </row>
     <row r="7">
@@ -702,25 +705,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7" t="n">
-        <v>0.024078</v>
+        <v>0.023556</v>
       </c>
       <c r="D7" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E7" t="n">
         <v>-2</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.02469</v>
+        <v>-0.02439</v>
       </c>
       <c r="G7" t="n">
-        <v>916</v>
+        <v>942</v>
       </c>
       <c r="H7" t="n">
-        <v>11.04</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="8">
@@ -728,25 +731,25 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>0.019917</v>
+        <v>0.019535</v>
       </c>
       <c r="D8" t="n">
         <v>68</v>
       </c>
       <c r="E8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01493</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>711</v>
+        <v>873</v>
       </c>
       <c r="H8" t="n">
-        <v>10.3</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="9">
@@ -754,25 +757,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01843</v>
+        <v>0.019247</v>
       </c>
       <c r="D9" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-0.01493</v>
       </c>
       <c r="G9" t="n">
-        <v>780</v>
+        <v>711</v>
       </c>
       <c r="H9" t="n">
-        <v>12.58</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="10">
@@ -780,25 +783,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>0.016647</v>
+        <v>0.016949</v>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
         <v>-1</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.01786</v>
+        <v>-0.01695</v>
       </c>
       <c r="G10" t="n">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="H10" t="n">
-        <v>12.47</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="11">
@@ -806,13 +809,13 @@
         <v>17</v>
       </c>
       <c r="B11" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C11" t="n">
-        <v>0.015458</v>
+        <v>0.0158</v>
       </c>
       <c r="D11" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -821,10 +824,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>396</v>
+        <v>454</v>
       </c>
       <c r="H11" t="n">
-        <v>7.62</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="12">
@@ -832,13 +835,13 @@
         <v>18</v>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" t="n">
-        <v>0.010999</v>
+        <v>0.010916</v>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -847,10 +850,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="H12" t="n">
-        <v>11.22</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="13">
@@ -858,25 +861,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>0.009512</v>
+        <v>0.009767</v>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.03125</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>712</v>
+        <v>160</v>
       </c>
       <c r="H13" t="n">
-        <v>21.58</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="14">
@@ -884,13 +887,13 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>0.008918</v>
+        <v>0.00948</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -899,10 +902,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>142</v>
+        <v>1338</v>
       </c>
       <c r="H14" t="n">
-        <v>4.73</v>
+        <v>40.55</v>
       </c>
     </row>
     <row r="15">
@@ -910,25 +913,25 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C15" t="n">
-        <v>0.008918</v>
+        <v>0.009193</v>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0.03125</v>
       </c>
       <c r="G15" t="n">
-        <v>1338</v>
+        <v>712</v>
       </c>
       <c r="H15" t="n">
-        <v>44.6</v>
+        <v>21.58</v>
       </c>
     </row>
     <row r="16">
@@ -936,13 +939,13 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C16" t="n">
-        <v>0.008323</v>
+        <v>0.008618</v>
       </c>
       <c r="D16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -951,10 +954,10 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="H16" t="n">
-        <v>9.14</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="17">
@@ -965,7 +968,7 @@
         <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>0.007134</v>
+        <v>0.006895</v>
       </c>
       <c r="D17" t="n">
         <v>24</v>
@@ -988,13 +991,13 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00654</v>
+        <v>0.006895</v>
       </c>
       <c r="D18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1003,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="H18" t="n">
-        <v>2.36</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="19">
@@ -1014,13 +1017,13 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>0.00654</v>
+        <v>0.006607</v>
       </c>
       <c r="D19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1029,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="H19" t="n">
-        <v>5.55</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="20">
@@ -1040,13 +1043,13 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>0.005945</v>
+        <v>0.006033</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1055,10 +1058,10 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>477</v>
+        <v>571</v>
       </c>
       <c r="H20" t="n">
-        <v>23.85</v>
+        <v>27.19</v>
       </c>
     </row>
     <row r="21">
@@ -1066,13 +1069,13 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>0.005351</v>
+        <v>0.005458</v>
       </c>
       <c r="D21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1081,10 +1084,10 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H21" t="n">
-        <v>5.67</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="22">
@@ -1092,13 +1095,13 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22" t="n">
-        <v>0.005054</v>
+        <v>0.005171</v>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1107,10 +1110,10 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="H22" t="n">
-        <v>6.12</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="23">
@@ -1118,13 +1121,13 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" t="n">
-        <v>0.005054</v>
+        <v>0.005171</v>
       </c>
       <c r="D23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1133,10 +1136,10 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="H23" t="n">
-        <v>6.59</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="24">
@@ -1144,25 +1147,25 @@
         <v>30</v>
       </c>
       <c r="B24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C24" t="n">
-        <v>0.004756</v>
+        <v>0.004884</v>
       </c>
       <c r="D24" t="n">
         <v>17</v>
       </c>
       <c r="E24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0625</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>230</v>
+        <v>127</v>
       </c>
       <c r="H24" t="n">
-        <v>13.53</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="25">
@@ -1170,25 +1173,25 @@
         <v>31</v>
       </c>
       <c r="B25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C25" t="n">
-        <v>0.004162</v>
+        <v>0.004596</v>
       </c>
       <c r="D25" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-0.0625</v>
       </c>
       <c r="G25" t="n">
-        <v>101</v>
+        <v>230</v>
       </c>
       <c r="H25" t="n">
-        <v>7.21</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="26">
@@ -1199,7 +1202,7 @@
         <v>13</v>
       </c>
       <c r="C26" t="n">
-        <v>0.003864</v>
+        <v>0.003735</v>
       </c>
       <c r="D26" t="n">
         <v>13</v>
@@ -1225,7 +1228,7 @@
         <v>12</v>
       </c>
       <c r="C27" t="n">
-        <v>0.003567</v>
+        <v>0.003447</v>
       </c>
       <c r="D27" t="n">
         <v>12</v>
@@ -1251,7 +1254,7 @@
         <v>12</v>
       </c>
       <c r="C28" t="n">
-        <v>0.003567</v>
+        <v>0.003447</v>
       </c>
       <c r="D28" t="n">
         <v>11</v>
@@ -1274,13 +1277,13 @@
         <v>35</v>
       </c>
       <c r="B29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002973</v>
+        <v>0.003447</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1289,10 +1292,10 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="H29" t="n">
-        <v>9.8</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="30">
@@ -1300,13 +1303,13 @@
         <v>36</v>
       </c>
       <c r="B30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C30" t="n">
-        <v>0.002675</v>
+        <v>0.002873</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1315,10 +1318,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>149</v>
+        <v>55</v>
       </c>
       <c r="H30" t="n">
-        <v>16.56</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="31">
@@ -1329,7 +1332,7 @@
         <v>9</v>
       </c>
       <c r="C31" t="n">
-        <v>0.002675</v>
+        <v>0.002585</v>
       </c>
       <c r="D31" t="n">
         <v>9</v>
@@ -1341,10 +1344,10 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="H31" t="n">
-        <v>15.56</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="32">
@@ -1355,7 +1358,7 @@
         <v>9</v>
       </c>
       <c r="C32" t="n">
-        <v>0.002675</v>
+        <v>0.002585</v>
       </c>
       <c r="D32" t="n">
         <v>9</v>
@@ -1367,10 +1370,10 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="H32" t="n">
-        <v>6.11</v>
+        <v>15.56</v>
       </c>
     </row>
     <row r="33">
@@ -1381,7 +1384,7 @@
         <v>8</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002378</v>
+        <v>0.002298</v>
       </c>
       <c r="D33" t="n">
         <v>8</v>
@@ -1407,7 +1410,7 @@
         <v>7</v>
       </c>
       <c r="C34" t="n">
-        <v>0.002081</v>
+        <v>0.002011</v>
       </c>
       <c r="D34" t="n">
         <v>7</v>
@@ -1419,10 +1422,10 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H34" t="n">
-        <v>1.43</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="35">
@@ -1433,7 +1436,7 @@
         <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001784</v>
+        <v>0.001724</v>
       </c>
       <c r="D35" t="n">
         <v>6</v>
@@ -1459,7 +1462,7 @@
         <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001486</v>
+        <v>0.001436</v>
       </c>
       <c r="D36" t="n">
         <v>5</v>
@@ -1485,7 +1488,7 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.001486</v>
+        <v>0.001436</v>
       </c>
       <c r="D37" t="n">
         <v>4</v>
@@ -1511,7 +1514,7 @@
         <v>5</v>
       </c>
       <c r="C38" t="n">
-        <v>0.001486</v>
+        <v>0.001436</v>
       </c>
       <c r="D38" t="n">
         <v>5</v>
@@ -1534,13 +1537,13 @@
         <v>45</v>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="n">
-        <v>0.001189</v>
+        <v>0.001436</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1552,7 +1555,7 @@
         <v>8</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="40">
@@ -1560,13 +1563,13 @@
         <v>46</v>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C40" t="n">
-        <v>0.000892</v>
+        <v>0.001436</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1575,10 +1578,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H40" t="n">
-        <v>15.67</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="41">
@@ -1586,13 +1589,13 @@
         <v>47</v>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>0.000892</v>
+        <v>0.001149</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -1601,10 +1604,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="H41" t="n">
-        <v>1.33</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="42">
@@ -1615,7 +1618,7 @@
         <v>3</v>
       </c>
       <c r="C42" t="n">
-        <v>0.000892</v>
+        <v>0.000862</v>
       </c>
       <c r="D42" t="n">
         <v>3</v>
@@ -1641,7 +1644,7 @@
         <v>3</v>
       </c>
       <c r="C43" t="n">
-        <v>0.000892</v>
+        <v>0.000862</v>
       </c>
       <c r="D43" t="n">
         <v>3</v>
@@ -1653,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H43" t="n">
-        <v>4.67</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="44">
@@ -1667,7 +1670,7 @@
         <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>0.000892</v>
+        <v>0.000862</v>
       </c>
       <c r="D44" t="n">
         <v>3</v>
@@ -1679,10 +1682,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="H44" t="n">
-        <v>16</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="45">
@@ -1693,7 +1696,7 @@
         <v>3</v>
       </c>
       <c r="C45" t="n">
-        <v>0.000892</v>
+        <v>0.000862</v>
       </c>
       <c r="D45" t="n">
         <v>3</v>
@@ -1705,10 +1708,10 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H45" t="n">
-        <v>1.67</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="46">
@@ -1716,13 +1719,13 @@
         <v>52</v>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" t="n">
-        <v>0.000595</v>
+        <v>0.000862</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -1731,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="47">
@@ -1745,7 +1748,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>0.000595</v>
+        <v>0.000575</v>
       </c>
       <c r="D47" t="n">
         <v>2</v>
@@ -1757,10 +1760,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H47" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1771,7 +1774,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>0.000595</v>
+        <v>0.000575</v>
       </c>
       <c r="D48" t="n">
         <v>2</v>
@@ -1783,10 +1786,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49">
@@ -1797,7 +1800,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>0.000595</v>
+        <v>0.000575</v>
       </c>
       <c r="D49" t="n">
         <v>2</v>
@@ -1809,10 +1812,10 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -1823,7 +1826,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>0.000595</v>
+        <v>0.000575</v>
       </c>
       <c r="D50" t="n">
         <v>2</v>
@@ -1849,7 +1852,7 @@
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0.000297</v>
+        <v>0.000287</v>
       </c>
       <c r="D51" t="n">
         <v>1</v>
@@ -1875,7 +1878,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.000297</v>
+        <v>0.000287</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
@@ -1901,7 +1904,7 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0.000297</v>
+        <v>0.000287</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
@@ -1927,7 +1930,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0.000297</v>
+        <v>0.000287</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
@@ -1953,7 +1956,7 @@
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>0.000297</v>
+        <v>0.000287</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
@@ -1979,7 +1982,7 @@
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>0.000297</v>
+        <v>0.000287</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
@@ -2005,7 +2008,7 @@
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>0.000297</v>
+        <v>0.000287</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
@@ -2031,7 +2034,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>0.000297</v>
+        <v>0.000287</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
@@ -2057,7 +2060,7 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.000297</v>
+        <v>0.000287</v>
       </c>
       <c r="D59" t="n">
         <v>1</v>
@@ -2069,10 +2072,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H59" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60">
@@ -2083,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>0.000297</v>
+        <v>0.000287</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
@@ -2095,9 +2098,35 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
+        <v>9</v>
+      </c>
+      <c r="H60" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.000287</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
         <v>6</v>
       </c>
-      <c r="H60" t="n">
+      <c r="H61" t="n">
         <v>6</v>
       </c>
     </row>
